--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1338B958-6E1E-459A-918D-EA1EAFB908C7}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB822F1C-C58E-43DA-A1A4-74EB883FFCE3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,7 +259,19 @@
     <t xml:space="preserve">low energy because of fresher's party </t>
   </si>
   <si>
-    <t>2026-09-</t>
+    <t>little bit tired</t>
+  </si>
+  <si>
+    <t>feel better because of holidays</t>
+  </si>
+  <si>
+    <t>very satisfied</t>
+  </si>
+  <si>
+    <t>good day</t>
+  </si>
+  <si>
+    <t>tired because more class</t>
   </si>
 </sst>
 </file>
@@ -959,7 +971,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="20">
-        <v>12603664</v>
+        <v>12603564</v>
       </c>
       <c r="G2" s="20"/>
     </row>
@@ -2016,94 +2028,188 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B28" s="14">
+        <v>300</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>200</v>
+      </c>
+      <c r="E28" s="14">
+        <v>120</v>
+      </c>
+      <c r="F28" s="14">
+        <v>250</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>20</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N28" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>40</v>
+      </c>
+      <c r="D29" s="14">
+        <v>400</v>
+      </c>
+      <c r="E29" s="14">
+        <v>300</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H29" s="14">
+        <v>30</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>250</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>360</v>
+      </c>
+      <c r="E30" s="14">
+        <v>300</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" s="14">
+        <v>40</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>290</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>320</v>
+      </c>
+      <c r="E31" s="14">
+        <v>200</v>
+      </c>
+      <c r="F31" s="14">
+        <v>300</v>
+      </c>
+      <c r="G31" s="14">
+        <v>6</v>
+      </c>
+      <c r="H31" s="14">
+        <v>20</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB822F1C-C58E-43DA-A1A4-74EB883FFCE3}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85A50B4-B397-4F7A-8F42-5F555BA82038}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,30 @@
   </si>
   <si>
     <t>tired because more class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it was good day </t>
+  </si>
+  <si>
+    <t xml:space="preserve">good day </t>
+  </si>
+  <si>
+    <t>just doing work of pg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complete the cls work </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ok ok </t>
+  </si>
+  <si>
+    <t xml:space="preserve">explore campus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">good because of holiday </t>
+  </si>
+  <si>
+    <t xml:space="preserve">visit new plaaces </t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1164,9 @@
       <c r="M7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
@@ -1184,7 +1210,9 @@
       <c r="M8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
@@ -1228,7 +1256,9 @@
       <c r="M9" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N9" s="17"/>
+      <c r="N9" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
@@ -1272,7 +1302,9 @@
       <c r="M10" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="17"/>
+      <c r="N10" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
@@ -1315,7 +1347,9 @@
       <c r="M11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="17"/>
+      <c r="N11" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
@@ -1359,7 +1393,9 @@
       <c r="M12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N12" s="17"/>
+      <c r="N12" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
@@ -1403,7 +1439,9 @@
       <c r="M13" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
@@ -1447,7 +1485,9 @@
       <c r="M14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N14" s="17"/>
+      <c r="N14" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
@@ -1491,7 +1531,9 @@
       <c r="M15" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="N15" s="17"/>
+      <c r="N15" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
@@ -1535,7 +1577,9 @@
       <c r="M16" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="N16" s="17"/>
+      <c r="N16" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
@@ -2212,26 +2256,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B32" s="14">
+        <v>300</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
+      <c r="D32" s="14">
+        <v>300</v>
+      </c>
+      <c r="E32" s="14">
+        <v>200</v>
+      </c>
+      <c r="F32" s="14">
+        <v>150</v>
+      </c>
+      <c r="G32" s="14">
+        <v>3</v>
+      </c>
+      <c r="H32" s="14">
+        <v>20</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85A50B4-B397-4F7A-8F42-5F555BA82038}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05BB591E-8329-4DFA-8E94-A310CD3EA8D3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,21 @@
   </si>
   <si>
     <t xml:space="preserve">visit new plaaces </t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>unsatisfied</t>
+  </si>
+  <si>
+    <t>to much pressure because of CA</t>
+  </si>
+  <si>
+    <t>Slept 3AM because CA</t>
+  </si>
+  <si>
+    <t>Tired because more classes</t>
   </si>
 </sst>
 </file>
@@ -2302,70 +2317,142 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B33" s="14">
+        <v>320</v>
+      </c>
+      <c r="C33" s="14">
+        <v>40</v>
+      </c>
+      <c r="D33" s="14">
+        <v>290</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>400</v>
+      </c>
+      <c r="G33" s="14">
+        <v>8</v>
+      </c>
+      <c r="H33" s="14">
+        <v>30</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>300</v>
+      </c>
+      <c r="E34" s="14">
+        <v>150</v>
+      </c>
+      <c r="F34" s="14">
+        <v>150</v>
+      </c>
+      <c r="G34" s="14">
+        <v>3</v>
+      </c>
+      <c r="H34" s="14">
+        <v>40</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B35" s="14">
+        <v>320</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>250</v>
+      </c>
+      <c r="E35" s="14">
+        <v>180</v>
+      </c>
+      <c r="F35" s="14">
+        <v>250</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>20</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05BB591E-8329-4DFA-8E94-A310CD3EA8D3}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9077158D-1114-435C-8D51-0598BFF322E3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Tired because more classes</t>
+  </si>
+  <si>
+    <t>Much pressure for CA slept 4AM</t>
   </si>
 </sst>
 </file>
@@ -2455,26 +2458,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B36" s="14">
+        <v>180</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>300</v>
+      </c>
+      <c r="E36" s="14">
+        <v>200</v>
+      </c>
+      <c r="F36" s="14">
+        <v>250</v>
+      </c>
+      <c r="G36" s="14">
+        <v>5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>30</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
